--- a/platform_PiN_output/Central_African_Republic___CAR/PiN_step1_Central_African_Republic___CAR_1009_08AM.xlsx
+++ b/platform_PiN_output/Central_African_Republic___CAR/PiN_step1_Central_African_Republic___CAR_1009_08AM.xlsx
@@ -1273,22 +1273,22 @@
         <v>547</v>
       </c>
       <c r="F4" s="30" t="n">
-        <v>47.9</v>
+        <v>47</v>
       </c>
       <c r="G4" s="30" t="n">
-        <v>817</v>
+        <v>802</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>11.6</v>
+        <v>8</v>
       </c>
       <c r="I4" s="30" t="n">
-        <v>197</v>
+        <v>136</v>
       </c>
       <c r="J4" s="30" t="n">
-        <v>8.5</v>
+        <v>12.9</v>
       </c>
       <c r="K4" s="30" t="n">
-        <v>144</v>
+        <v>220</v>
       </c>
       <c r="L4" s="30" t="n">
         <v>67.90000000000001</v>
@@ -1447,16 +1447,16 @@
         <v>560</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>8.9</v>
+        <v>7.1</v>
       </c>
       <c r="I5" s="30" t="n">
-        <v>190</v>
+        <v>152</v>
       </c>
       <c r="J5" s="30" t="n">
-        <v>4</v>
+        <v>5.8</v>
       </c>
       <c r="K5" s="30" t="n">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="L5" s="30" t="n">
         <v>39.1</v>
@@ -1609,10 +1609,10 @@
         <v>3829</v>
       </c>
       <c r="F6" s="30" t="n">
-        <v>26.2</v>
+        <v>25</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>1546</v>
+        <v>1474</v>
       </c>
       <c r="H6" s="30" t="n">
         <v>1.4</v>
@@ -1621,10 +1621,10 @@
         <v>80</v>
       </c>
       <c r="J6" s="30" t="n">
-        <v>7.4</v>
+        <v>8.6</v>
       </c>
       <c r="K6" s="30" t="n">
-        <v>435</v>
+        <v>508</v>
       </c>
       <c r="L6" s="30" t="n">
         <v>35</v>
@@ -2329,10 +2329,10 @@
         <v>85</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>28</v>
+        <v>27.6</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="H10" s="30" t="n">
         <v>19</v>
@@ -2341,10 +2341,10 @@
         <v>106</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>37.7</v>
+        <v>38</v>
       </c>
       <c r="K10" s="30" t="n">
-        <v>209</v>
+        <v>211</v>
       </c>
       <c r="L10" s="30" t="n">
         <v>84.7</v>
@@ -3041,22 +3041,22 @@
         <v>3491</v>
       </c>
       <c r="F14" s="30" t="n">
-        <v>11.8</v>
+        <v>11.6</v>
       </c>
       <c r="G14" s="30" t="n">
-        <v>775</v>
+        <v>760</v>
       </c>
       <c r="H14" s="30" t="n">
-        <v>15.5</v>
+        <v>14.6</v>
       </c>
       <c r="I14" s="30" t="n">
-        <v>1020</v>
+        <v>956</v>
       </c>
       <c r="J14" s="30" t="n">
-        <v>19.4</v>
+        <v>20.6</v>
       </c>
       <c r="K14" s="30" t="n">
-        <v>1275</v>
+        <v>1353</v>
       </c>
       <c r="L14" s="30" t="n">
         <v>46.8</v>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="N14" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O14" s="32" t="n">
@@ -3219,22 +3219,22 @@
         <v>3348</v>
       </c>
       <c r="F15" s="30" t="n">
-        <v>16.3</v>
+        <v>14.8</v>
       </c>
       <c r="G15" s="30" t="n">
-        <v>923</v>
+        <v>839</v>
       </c>
       <c r="H15" s="30" t="n">
-        <v>8.5</v>
+        <v>7.7</v>
       </c>
       <c r="I15" s="30" t="n">
-        <v>482</v>
+        <v>437</v>
       </c>
       <c r="J15" s="30" t="n">
-        <v>16.2</v>
+        <v>18.4</v>
       </c>
       <c r="K15" s="30" t="n">
-        <v>917</v>
+        <v>1046</v>
       </c>
       <c r="L15" s="30" t="n">
         <v>41</v>
@@ -3397,22 +3397,22 @@
         <v>224</v>
       </c>
       <c r="F16" s="30" t="n">
-        <v>21.5</v>
+        <v>20.2</v>
       </c>
       <c r="G16" s="30" t="n">
-        <v>157</v>
+        <v>147</v>
       </c>
       <c r="H16" s="30" t="n">
-        <v>34.2</v>
+        <v>32.7</v>
       </c>
       <c r="I16" s="30" t="n">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="J16" s="30" t="n">
-        <v>13.5</v>
+        <v>16.3</v>
       </c>
       <c r="K16" s="30" t="n">
-        <v>98</v>
+        <v>119</v>
       </c>
       <c r="L16" s="30" t="n">
         <v>69.2</v>
@@ -3575,22 +3575,22 @@
         <v>748</v>
       </c>
       <c r="F17" s="30" t="n">
-        <v>18</v>
+        <v>14.9</v>
       </c>
       <c r="G17" s="30" t="n">
-        <v>388</v>
+        <v>321</v>
       </c>
       <c r="H17" s="30" t="n">
-        <v>35.2</v>
+        <v>31.5</v>
       </c>
       <c r="I17" s="30" t="n">
-        <v>761</v>
+        <v>681</v>
       </c>
       <c r="J17" s="30" t="n">
-        <v>12.2</v>
+        <v>19</v>
       </c>
       <c r="K17" s="30" t="n">
-        <v>264</v>
+        <v>410</v>
       </c>
       <c r="L17" s="30" t="n">
         <v>65.40000000000001</v>
@@ -3931,22 +3931,22 @@
         <v>2733</v>
       </c>
       <c r="F19" s="30" t="n">
-        <v>29</v>
+        <v>26.7</v>
       </c>
       <c r="G19" s="30" t="n">
-        <v>1481</v>
+        <v>1365</v>
       </c>
       <c r="H19" s="30" t="n">
-        <v>10</v>
+        <v>7.9</v>
       </c>
       <c r="I19" s="30" t="n">
-        <v>509</v>
+        <v>401</v>
       </c>
       <c r="J19" s="30" t="n">
-        <v>7.5</v>
+        <v>11.9</v>
       </c>
       <c r="K19" s="30" t="n">
-        <v>385</v>
+        <v>609</v>
       </c>
       <c r="L19" s="30" t="n">
         <v>46.5</v>
@@ -4123,10 +4123,10 @@
         <v>2522</v>
       </c>
       <c r="F20" s="30" t="n">
-        <v>23.7</v>
+        <v>23.5</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>1103</v>
+        <v>1093</v>
       </c>
       <c r="H20" s="30" t="n">
         <v>17.1</v>
@@ -4135,10 +4135,10 @@
         <v>798</v>
       </c>
       <c r="J20" s="30" t="n">
-        <v>5.1</v>
+        <v>5.3</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>236</v>
+        <v>246</v>
       </c>
       <c r="L20" s="30" t="n">
         <v>45.9</v>
@@ -4301,22 +4301,22 @@
         <v>2567</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>27.8</v>
+        <v>25.8</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>1402</v>
+        <v>1300</v>
       </c>
       <c r="H21" s="30" t="n">
-        <v>8.300000000000001</v>
+        <v>8.1</v>
       </c>
       <c r="I21" s="30" t="n">
-        <v>417</v>
+        <v>407</v>
       </c>
       <c r="J21" s="30" t="n">
-        <v>13.1</v>
+        <v>15.3</v>
       </c>
       <c r="K21" s="30" t="n">
-        <v>661</v>
+        <v>772</v>
       </c>
       <c r="L21" s="30" t="n">
         <v>49.1</v>
@@ -4479,10 +4479,10 @@
         <v>14103</v>
       </c>
       <c r="F22" s="30" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="G22" s="30" t="n">
-        <v>4029</v>
+        <v>3987</v>
       </c>
       <c r="H22" s="30" t="n">
         <v>2.2</v>
@@ -4491,10 +4491,10 @@
         <v>443</v>
       </c>
       <c r="J22" s="30" t="n">
-        <v>8.4</v>
+        <v>8.6</v>
       </c>
       <c r="K22" s="30" t="n">
-        <v>1695</v>
+        <v>1737</v>
       </c>
       <c r="L22" s="30" t="n">
         <v>30.4</v>
@@ -4657,10 +4657,10 @@
         <v>5435</v>
       </c>
       <c r="F23" s="30" t="n">
-        <v>18.5</v>
+        <v>16.7</v>
       </c>
       <c r="G23" s="30" t="n">
-        <v>1887</v>
+        <v>1703</v>
       </c>
       <c r="H23" s="30" t="n">
         <v>13.4</v>
@@ -4669,10 +4669,10 @@
         <v>1370</v>
       </c>
       <c r="J23" s="30" t="n">
-        <v>14.8</v>
+        <v>16.6</v>
       </c>
       <c r="K23" s="30" t="n">
-        <v>1509</v>
+        <v>1693</v>
       </c>
       <c r="L23" s="30" t="n">
         <v>46.7</v>
@@ -4835,22 +4835,22 @@
         <v>2558</v>
       </c>
       <c r="F24" s="30" t="n">
-        <v>26.4</v>
+        <v>25.3</v>
       </c>
       <c r="G24" s="30" t="n">
-        <v>2422</v>
+        <v>2325</v>
       </c>
       <c r="H24" s="30" t="n">
-        <v>24.3</v>
+        <v>21.6</v>
       </c>
       <c r="I24" s="30" t="n">
-        <v>2228</v>
+        <v>1982</v>
       </c>
       <c r="J24" s="30" t="n">
-        <v>21.5</v>
+        <v>25.2</v>
       </c>
       <c r="K24" s="30" t="n">
-        <v>1970</v>
+        <v>2313</v>
       </c>
       <c r="L24" s="30" t="n">
         <v>72.09999999999999</v>
@@ -5013,10 +5013,10 @@
         <v>687</v>
       </c>
       <c r="F25" s="30" t="n">
-        <v>29.1</v>
+        <v>27.4</v>
       </c>
       <c r="G25" s="30" t="n">
-        <v>528</v>
+        <v>496</v>
       </c>
       <c r="H25" s="30" t="n">
         <v>16.6</v>
@@ -5025,10 +5025,10 @@
         <v>300</v>
       </c>
       <c r="J25" s="30" t="n">
-        <v>16.4</v>
+        <v>18.2</v>
       </c>
       <c r="K25" s="30" t="n">
-        <v>297</v>
+        <v>329</v>
       </c>
       <c r="L25" s="30" t="n">
         <v>62.1</v>
@@ -5191,22 +5191,22 @@
         <v>1793</v>
       </c>
       <c r="F26" s="30" t="n">
-        <v>27</v>
+        <v>26.1</v>
       </c>
       <c r="G26" s="30" t="n">
-        <v>1186</v>
+        <v>1144</v>
       </c>
       <c r="H26" s="30" t="n">
-        <v>22.3</v>
+        <v>19.9</v>
       </c>
       <c r="I26" s="30" t="n">
-        <v>977</v>
+        <v>875</v>
       </c>
       <c r="J26" s="30" t="n">
-        <v>9.800000000000001</v>
+        <v>13.1</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>430</v>
+        <v>574</v>
       </c>
       <c r="L26" s="30" t="n">
         <v>59.1</v>
@@ -5369,22 +5369,22 @@
         <v>183</v>
       </c>
       <c r="F27" s="30" t="n">
-        <v>25.5</v>
+        <v>24.1</v>
       </c>
       <c r="G27" s="30" t="n">
-        <v>76</v>
+        <v>71</v>
       </c>
       <c r="H27" s="30" t="n">
-        <v>7.4</v>
+        <v>4.2</v>
       </c>
       <c r="I27" s="30" t="n">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J27" s="30" t="n">
-        <v>5.5</v>
+        <v>10.2</v>
       </c>
       <c r="K27" s="30" t="n">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="L27" s="30" t="n">
         <v>38.5</v>
@@ -5547,22 +5547,22 @@
         <v>237</v>
       </c>
       <c r="F28" s="30" t="n">
-        <v>17</v>
+        <v>15.4</v>
       </c>
       <c r="G28" s="30" t="n">
-        <v>76</v>
+        <v>69</v>
       </c>
       <c r="H28" s="30" t="n">
-        <v>21.9</v>
+        <v>19.2</v>
       </c>
       <c r="I28" s="30" t="n">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="J28" s="30" t="n">
-        <v>8</v>
+        <v>12.3</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>36</v>
+        <v>55</v>
       </c>
       <c r="L28" s="30" t="n">
         <v>46.9</v>
@@ -5731,16 +5731,16 @@
         <v>90</v>
       </c>
       <c r="H29" s="30" t="n">
-        <v>11.6</v>
+        <v>10.1</v>
       </c>
       <c r="I29" s="30" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="J29" s="30" t="n">
-        <v>7.2</v>
+        <v>8.6</v>
       </c>
       <c r="K29" s="30" t="n">
-        <v>18</v>
+        <v>22</v>
       </c>
       <c r="L29" s="30" t="n">
         <v>54.1</v>
@@ -5903,22 +5903,22 @@
         <v>493</v>
       </c>
       <c r="F30" s="30" t="n">
-        <v>32.8</v>
+        <v>30.6</v>
       </c>
       <c r="G30" s="30" t="n">
-        <v>423</v>
+        <v>394</v>
       </c>
       <c r="H30" s="30" t="n">
-        <v>21.5</v>
+        <v>19.9</v>
       </c>
       <c r="I30" s="30" t="n">
-        <v>277</v>
+        <v>256</v>
       </c>
       <c r="J30" s="30" t="n">
-        <v>7.4</v>
+        <v>11.3</v>
       </c>
       <c r="K30" s="30" t="n">
-        <v>95</v>
+        <v>146</v>
       </c>
       <c r="L30" s="30" t="n">
         <v>61.7</v>
@@ -6081,10 +6081,10 @@
         <v>896</v>
       </c>
       <c r="F31" s="30" t="n">
-        <v>19.6</v>
+        <v>18.9</v>
       </c>
       <c r="G31" s="30" t="n">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="H31" s="30" t="n">
         <v>6.8</v>
@@ -6093,10 +6093,10 @@
         <v>87</v>
       </c>
       <c r="J31" s="30" t="n">
-        <v>3.5</v>
+        <v>4.3</v>
       </c>
       <c r="K31" s="30" t="n">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="L31" s="30" t="n">
         <v>30</v>
@@ -6259,22 +6259,22 @@
         <v>2877</v>
       </c>
       <c r="F32" s="30" t="n">
-        <v>27.1</v>
+        <v>22.7</v>
       </c>
       <c r="G32" s="30" t="n">
-        <v>1369</v>
+        <v>1148</v>
       </c>
       <c r="H32" s="30" t="n">
-        <v>5.7</v>
+        <v>1.1</v>
       </c>
       <c r="I32" s="30" t="n">
-        <v>290</v>
+        <v>56</v>
       </c>
       <c r="J32" s="30" t="n">
-        <v>10.2</v>
+        <v>19.2</v>
       </c>
       <c r="K32" s="30" t="n">
-        <v>517</v>
+        <v>972</v>
       </c>
       <c r="L32" s="30" t="n">
         <v>43.1</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="N32" s="31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O32" s="32" t="n">
@@ -6437,22 +6437,22 @@
         <v>585</v>
       </c>
       <c r="F33" s="30" t="n">
-        <v>36.3</v>
+        <v>29.9</v>
       </c>
       <c r="G33" s="30" t="n">
-        <v>496</v>
+        <v>409</v>
       </c>
       <c r="H33" s="30" t="n">
-        <v>6.8</v>
+        <v>6</v>
       </c>
       <c r="I33" s="30" t="n">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="J33" s="30" t="n">
-        <v>14.1</v>
+        <v>21.3</v>
       </c>
       <c r="K33" s="30" t="n">
-        <v>194</v>
+        <v>292</v>
       </c>
       <c r="L33" s="30" t="n">
         <v>57.2</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="N33" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O33" s="32" t="n">
@@ -6615,22 +6615,22 @@
         <v>546</v>
       </c>
       <c r="F34" s="30" t="n">
-        <v>20.2</v>
+        <v>19.2</v>
       </c>
       <c r="G34" s="30" t="n">
-        <v>610</v>
+        <v>581</v>
       </c>
       <c r="H34" s="30" t="n">
-        <v>48.8</v>
+        <v>37.7</v>
       </c>
       <c r="I34" s="30" t="n">
-        <v>1475</v>
+        <v>1139</v>
       </c>
       <c r="J34" s="30" t="n">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="K34" s="30" t="n">
-        <v>393</v>
+        <v>757</v>
       </c>
       <c r="L34" s="30" t="n">
         <v>81.90000000000001</v>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="N34" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O34" s="32" t="n">
@@ -6980,13 +6980,13 @@
         <v>1.5</v>
       </c>
       <c r="I36" s="30" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="J36" s="30" t="n">
-        <v>6.9</v>
+        <v>7</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="L36" s="30" t="n">
         <v>26.7</v>
@@ -7327,10 +7327,10 @@
         <v>14103</v>
       </c>
       <c r="F38" s="30" t="n">
-        <v>18.6</v>
+        <v>17</v>
       </c>
       <c r="G38" s="30" t="n">
-        <v>4023</v>
+        <v>3674</v>
       </c>
       <c r="H38" s="30" t="n">
         <v>9.199999999999999</v>
@@ -7339,10 +7339,10 @@
         <v>1984</v>
       </c>
       <c r="J38" s="30" t="n">
-        <v>7</v>
+        <v>8.6</v>
       </c>
       <c r="K38" s="30" t="n">
-        <v>1516</v>
+        <v>1865</v>
       </c>
       <c r="L38" s="30" t="n">
         <v>34.8</v>
@@ -7505,22 +7505,22 @@
         <v>1595</v>
       </c>
       <c r="F39" s="30" t="n">
-        <v>26.5</v>
+        <v>19.5</v>
       </c>
       <c r="G39" s="30" t="n">
-        <v>1236</v>
+        <v>910</v>
       </c>
       <c r="H39" s="30" t="n">
+        <v>20.4</v>
+      </c>
+      <c r="I39" s="30" t="n">
+        <v>950</v>
+      </c>
+      <c r="J39" s="30" t="n">
         <v>26</v>
       </c>
-      <c r="I39" s="30" t="n">
+      <c r="K39" s="30" t="n">
         <v>1215</v>
-      </c>
-      <c r="J39" s="30" t="n">
-        <v>13.4</v>
-      </c>
-      <c r="K39" s="30" t="n">
-        <v>624</v>
       </c>
       <c r="L39" s="30" t="n">
         <v>65.90000000000001</v>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="N39" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O39" s="32" t="n">
@@ -7683,22 +7683,22 @@
         <v>9241</v>
       </c>
       <c r="F40" s="30" t="n">
-        <v>14.2</v>
+        <v>13.6</v>
       </c>
       <c r="G40" s="30" t="n">
-        <v>1781</v>
+        <v>1712</v>
       </c>
       <c r="H40" s="30" t="n">
-        <v>5.2</v>
+        <v>4.6</v>
       </c>
       <c r="I40" s="30" t="n">
-        <v>648</v>
+        <v>580</v>
       </c>
       <c r="J40" s="30" t="n">
-        <v>7.1</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="K40" s="30" t="n">
-        <v>898</v>
+        <v>1035</v>
       </c>
       <c r="L40" s="30" t="n">
         <v>26.5</v>
@@ -7861,22 +7861,22 @@
         <v>4589</v>
       </c>
       <c r="F41" s="30" t="n">
-        <v>24.9</v>
+        <v>24.2</v>
       </c>
       <c r="G41" s="30" t="n">
-        <v>1681</v>
+        <v>1639</v>
       </c>
       <c r="H41" s="30" t="n">
-        <v>2.3</v>
+        <v>2.2</v>
       </c>
       <c r="I41" s="30" t="n">
-        <v>152</v>
+        <v>147</v>
       </c>
       <c r="J41" s="30" t="n">
-        <v>5</v>
+        <v>5.7</v>
       </c>
       <c r="K41" s="30" t="n">
-        <v>341</v>
+        <v>389</v>
       </c>
       <c r="L41" s="30" t="n">
         <v>32.2</v>
@@ -8217,22 +8217,22 @@
         <v>8418</v>
       </c>
       <c r="F43" s="30" t="n">
-        <v>21.2</v>
+        <v>20.4</v>
       </c>
       <c r="G43" s="30" t="n">
-        <v>2872</v>
+        <v>2752</v>
       </c>
       <c r="H43" s="30" t="n">
-        <v>0.9</v>
+        <v>0.8</v>
       </c>
       <c r="I43" s="30" t="n">
-        <v>127</v>
+        <v>105</v>
       </c>
       <c r="J43" s="30" t="n">
-        <v>15.5</v>
+        <v>16.6</v>
       </c>
       <c r="K43" s="30" t="n">
-        <v>2100</v>
+        <v>2242</v>
       </c>
       <c r="L43" s="30" t="n">
         <v>37.7</v>
@@ -8401,16 +8401,16 @@
         <v>584</v>
       </c>
       <c r="H44" s="30" t="n">
-        <v>10.2</v>
+        <v>8.9</v>
       </c>
       <c r="I44" s="30" t="n">
-        <v>141</v>
+        <v>123</v>
       </c>
       <c r="J44" s="30" t="n">
-        <v>9.5</v>
+        <v>10.8</v>
       </c>
       <c r="K44" s="30" t="n">
-        <v>132</v>
+        <v>150</v>
       </c>
       <c r="L44" s="30" t="n">
         <v>61.7</v>
@@ -8573,22 +8573,22 @@
         <v>30</v>
       </c>
       <c r="F45" s="30" t="n">
-        <v>30.6</v>
+        <v>30</v>
       </c>
       <c r="G45" s="30" t="n">
         <v>25</v>
       </c>
       <c r="H45" s="30" t="n">
-        <v>20.6</v>
+        <v>17.1</v>
       </c>
       <c r="I45" s="30" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J45" s="30" t="n">
-        <v>12.5</v>
+        <v>16.5</v>
       </c>
       <c r="K45" s="30" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="L45" s="30" t="n">
         <v>63.7</v>
@@ -9295,10 +9295,10 @@
         <v>3024</v>
       </c>
       <c r="F49" s="30" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="G49" s="30" t="n">
-        <v>817</v>
+        <v>809</v>
       </c>
       <c r="H49" s="30" t="n">
         <v>6</v>
@@ -9307,10 +9307,10 @@
         <v>260</v>
       </c>
       <c r="J49" s="30" t="n">
-        <v>5.9</v>
+        <v>6.1</v>
       </c>
       <c r="K49" s="30" t="n">
-        <v>259</v>
+        <v>266</v>
       </c>
       <c r="L49" s="30" t="n">
         <v>30.6</v>
@@ -9473,22 +9473,22 @@
         <v>5647</v>
       </c>
       <c r="F50" s="30" t="n">
-        <v>26</v>
+        <v>24.5</v>
       </c>
       <c r="G50" s="30" t="n">
-        <v>2934</v>
+        <v>2771</v>
       </c>
       <c r="H50" s="30" t="n">
-        <v>7.1</v>
+        <v>5.7</v>
       </c>
       <c r="I50" s="30" t="n">
-        <v>797</v>
+        <v>638</v>
       </c>
       <c r="J50" s="30" t="n">
-        <v>17</v>
+        <v>19.8</v>
       </c>
       <c r="K50" s="30" t="n">
-        <v>1916</v>
+        <v>2239</v>
       </c>
       <c r="L50" s="30" t="n">
         <v>50</v>
@@ -9829,10 +9829,10 @@
         <v>3400</v>
       </c>
       <c r="F52" s="30" t="n">
-        <v>32</v>
+        <v>31.3</v>
       </c>
       <c r="G52" s="30" t="n">
-        <v>2245</v>
+        <v>2198</v>
       </c>
       <c r="H52" s="30" t="n">
         <v>5.8</v>
@@ -9841,10 +9841,10 @@
         <v>407</v>
       </c>
       <c r="J52" s="30" t="n">
-        <v>13.8</v>
+        <v>14.4</v>
       </c>
       <c r="K52" s="30" t="n">
-        <v>967</v>
+        <v>1014</v>
       </c>
       <c r="L52" s="30" t="n">
         <v>51.6</v>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="N52" s="31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O52" s="32" t="n">
@@ -10007,22 +10007,22 @@
         <v>174</v>
       </c>
       <c r="F53" s="30" t="n">
-        <v>36.9</v>
+        <v>36.7</v>
       </c>
       <c r="G53" s="30" t="n">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="H53" s="30" t="n">
-        <v>6</v>
+        <v>5.2</v>
       </c>
       <c r="I53" s="30" t="n">
-        <v>43</v>
+        <v>37</v>
       </c>
       <c r="J53" s="30" t="n">
-        <v>32.7</v>
+        <v>33.6</v>
       </c>
       <c r="K53" s="30" t="n">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="L53" s="30" t="n">
         <v>75.59999999999999</v>
@@ -10205,22 +10205,22 @@
         <v>1006</v>
       </c>
       <c r="F54" s="30" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="G54" s="30" t="n">
-        <v>309</v>
+        <v>306</v>
       </c>
       <c r="H54" s="30" t="n">
-        <v>3.8</v>
+        <v>3</v>
       </c>
       <c r="I54" s="30" t="n">
-        <v>58</v>
+        <v>46</v>
       </c>
       <c r="J54" s="30" t="n">
-        <v>10.3</v>
+        <v>11.3</v>
       </c>
       <c r="K54" s="30" t="n">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="L54" s="30" t="n">
         <v>34.3</v>
@@ -10561,22 +10561,22 @@
         <v>290</v>
       </c>
       <c r="F56" s="30" t="n">
-        <v>27.3</v>
+        <v>26.7</v>
       </c>
       <c r="G56" s="30" t="n">
-        <v>258</v>
+        <v>253</v>
       </c>
       <c r="H56" s="30" t="n">
-        <v>14.9</v>
+        <v>12</v>
       </c>
       <c r="I56" s="30" t="n">
-        <v>141</v>
+        <v>113</v>
       </c>
       <c r="J56" s="30" t="n">
-        <v>27.2</v>
+        <v>30.7</v>
       </c>
       <c r="K56" s="30" t="n">
-        <v>257</v>
+        <v>290</v>
       </c>
       <c r="L56" s="30" t="n">
         <v>69.40000000000001</v>
@@ -10739,22 +10739,22 @@
         <v>2349</v>
       </c>
       <c r="F57" s="30" t="n">
-        <v>20.7</v>
+        <v>20.2</v>
       </c>
       <c r="G57" s="30" t="n">
-        <v>771</v>
+        <v>752</v>
       </c>
       <c r="H57" s="30" t="n">
-        <v>4.4</v>
+        <v>3.6</v>
       </c>
       <c r="I57" s="30" t="n">
-        <v>162</v>
+        <v>133</v>
       </c>
       <c r="J57" s="30" t="n">
-        <v>11.8</v>
+        <v>13.1</v>
       </c>
       <c r="K57" s="30" t="n">
-        <v>439</v>
+        <v>487</v>
       </c>
       <c r="L57" s="30" t="n">
         <v>36.9</v>
@@ -10917,22 +10917,22 @@
         <v>3969</v>
       </c>
       <c r="F58" s="30" t="n">
-        <v>25.4</v>
+        <v>24.9</v>
       </c>
       <c r="G58" s="30" t="n">
-        <v>1783</v>
+        <v>1751</v>
       </c>
       <c r="H58" s="30" t="n">
-        <v>10.3</v>
+        <v>9.5</v>
       </c>
       <c r="I58" s="30" t="n">
-        <v>722</v>
+        <v>668</v>
       </c>
       <c r="J58" s="30" t="n">
-        <v>7.8</v>
+        <v>9</v>
       </c>
       <c r="K58" s="30" t="n">
-        <v>547</v>
+        <v>633</v>
       </c>
       <c r="L58" s="30" t="n">
         <v>43.5</v>
@@ -11095,10 +11095,10 @@
         <v>2787</v>
       </c>
       <c r="F59" s="30" t="n">
-        <v>32.9</v>
+        <v>32.1</v>
       </c>
       <c r="G59" s="30" t="n">
-        <v>1701</v>
+        <v>1661</v>
       </c>
       <c r="H59" s="30" t="n">
         <v>4.9</v>
@@ -11107,10 +11107,10 @@
         <v>253</v>
       </c>
       <c r="J59" s="30" t="n">
-        <v>8.300000000000001</v>
+        <v>9.1</v>
       </c>
       <c r="K59" s="30" t="n">
-        <v>428</v>
+        <v>468</v>
       </c>
       <c r="L59" s="30" t="n">
         <v>46.1</v>
@@ -11469,22 +11469,22 @@
         <v>974</v>
       </c>
       <c r="F61" s="30" t="n">
-        <v>52.8</v>
+        <v>29.8</v>
       </c>
       <c r="G61" s="30" t="n">
-        <v>2162</v>
+        <v>1219</v>
       </c>
       <c r="H61" s="30" t="n">
-        <v>16</v>
+        <v>13.5</v>
       </c>
       <c r="I61" s="30" t="n">
-        <v>654</v>
+        <v>554</v>
       </c>
       <c r="J61" s="30" t="n">
-        <v>7.5</v>
+        <v>32.9</v>
       </c>
       <c r="K61" s="30" t="n">
-        <v>308</v>
+        <v>1350</v>
       </c>
       <c r="L61" s="30" t="n">
         <v>76.2</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="N61" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="O61" s="32" t="n">
@@ -11843,22 +11843,22 @@
         <v>234</v>
       </c>
       <c r="F63" s="30" t="n">
-        <v>28.2</v>
+        <v>25.4</v>
       </c>
       <c r="G63" s="30" t="n">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="H63" s="30" t="n">
-        <v>19.7</v>
+        <v>18.3</v>
       </c>
       <c r="I63" s="30" t="n">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="J63" s="30" t="n">
-        <v>9.9</v>
+        <v>14.1</v>
       </c>
       <c r="K63" s="30" t="n">
-        <v>54</v>
+        <v>78</v>
       </c>
       <c r="L63" s="30" t="n">
         <v>57.7</v>
@@ -12397,22 +12397,22 @@
         <v>20435</v>
       </c>
       <c r="F66" s="30" t="n">
-        <v>8.199999999999999</v>
+        <v>8</v>
       </c>
       <c r="G66" s="30" t="n">
-        <v>2869</v>
+        <v>2804</v>
       </c>
       <c r="H66" s="30" t="n">
-        <v>27.8</v>
+        <v>26.9</v>
       </c>
       <c r="I66" s="30" t="n">
-        <v>9765</v>
+        <v>9459</v>
       </c>
       <c r="J66" s="30" t="n">
-        <v>5.8</v>
+        <v>6.9</v>
       </c>
       <c r="K66" s="30" t="n">
-        <v>2045</v>
+        <v>2416</v>
       </c>
       <c r="L66" s="30" t="n">
         <v>41.8</v>

--- a/platform_PiN_output/Central_African_Republic___CAR/PiN_step1_Central_African_Republic___CAR_1009_08AM.xlsx
+++ b/platform_PiN_output/Central_African_Republic___CAR/PiN_step1_Central_African_Republic___CAR_1009_08AM.xlsx
@@ -1273,22 +1273,22 @@
         <v>547</v>
       </c>
       <c r="F4" s="30" t="n">
-        <v>47</v>
+        <v>47.9</v>
       </c>
       <c r="G4" s="30" t="n">
-        <v>802</v>
+        <v>817</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>8</v>
+        <v>11.6</v>
       </c>
       <c r="I4" s="30" t="n">
-        <v>136</v>
+        <v>197</v>
       </c>
       <c r="J4" s="30" t="n">
-        <v>12.9</v>
+        <v>8.5</v>
       </c>
       <c r="K4" s="30" t="n">
-        <v>220</v>
+        <v>144</v>
       </c>
       <c r="L4" s="30" t="n">
         <v>67.90000000000001</v>
@@ -1447,16 +1447,16 @@
         <v>560</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>7.1</v>
+        <v>8.9</v>
       </c>
       <c r="I5" s="30" t="n">
-        <v>152</v>
+        <v>190</v>
       </c>
       <c r="J5" s="30" t="n">
-        <v>5.8</v>
+        <v>4</v>
       </c>
       <c r="K5" s="30" t="n">
-        <v>123</v>
+        <v>85</v>
       </c>
       <c r="L5" s="30" t="n">
         <v>39.1</v>
@@ -1609,10 +1609,10 @@
         <v>3829</v>
       </c>
       <c r="F6" s="30" t="n">
-        <v>25</v>
+        <v>26.2</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>1474</v>
+        <v>1546</v>
       </c>
       <c r="H6" s="30" t="n">
         <v>1.4</v>
@@ -1621,10 +1621,10 @@
         <v>80</v>
       </c>
       <c r="J6" s="30" t="n">
-        <v>8.6</v>
+        <v>7.4</v>
       </c>
       <c r="K6" s="30" t="n">
-        <v>508</v>
+        <v>435</v>
       </c>
       <c r="L6" s="30" t="n">
         <v>35</v>
@@ -2329,10 +2329,10 @@
         <v>85</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>27.6</v>
+        <v>28</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>154</v>
+        <v>155</v>
       </c>
       <c r="H10" s="30" t="n">
         <v>19</v>
@@ -2341,10 +2341,10 @@
         <v>106</v>
       </c>
       <c r="J10" s="30" t="n">
-        <v>38</v>
+        <v>37.7</v>
       </c>
       <c r="K10" s="30" t="n">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="L10" s="30" t="n">
         <v>84.7</v>
@@ -3041,22 +3041,22 @@
         <v>3491</v>
       </c>
       <c r="F14" s="30" t="n">
-        <v>11.6</v>
+        <v>11.8</v>
       </c>
       <c r="G14" s="30" t="n">
-        <v>760</v>
+        <v>775</v>
       </c>
       <c r="H14" s="30" t="n">
-        <v>14.6</v>
+        <v>15.5</v>
       </c>
       <c r="I14" s="30" t="n">
-        <v>956</v>
+        <v>1020</v>
       </c>
       <c r="J14" s="30" t="n">
-        <v>20.6</v>
+        <v>19.4</v>
       </c>
       <c r="K14" s="30" t="n">
-        <v>1353</v>
+        <v>1275</v>
       </c>
       <c r="L14" s="30" t="n">
         <v>46.8</v>
@@ -3066,7 +3066,7 @@
       </c>
       <c r="N14" s="31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O14" s="32" t="n">
@@ -3219,22 +3219,22 @@
         <v>3348</v>
       </c>
       <c r="F15" s="30" t="n">
-        <v>14.8</v>
+        <v>16.3</v>
       </c>
       <c r="G15" s="30" t="n">
-        <v>839</v>
+        <v>923</v>
       </c>
       <c r="H15" s="30" t="n">
-        <v>7.7</v>
+        <v>8.5</v>
       </c>
       <c r="I15" s="30" t="n">
-        <v>437</v>
+        <v>482</v>
       </c>
       <c r="J15" s="30" t="n">
-        <v>18.4</v>
+        <v>16.2</v>
       </c>
       <c r="K15" s="30" t="n">
-        <v>1046</v>
+        <v>917</v>
       </c>
       <c r="L15" s="30" t="n">
         <v>41</v>
@@ -3397,22 +3397,22 @@
         <v>224</v>
       </c>
       <c r="F16" s="30" t="n">
-        <v>20.2</v>
+        <v>21.5</v>
       </c>
       <c r="G16" s="30" t="n">
-        <v>147</v>
+        <v>157</v>
       </c>
       <c r="H16" s="30" t="n">
-        <v>32.7</v>
+        <v>34.2</v>
       </c>
       <c r="I16" s="30" t="n">
-        <v>237</v>
+        <v>248</v>
       </c>
       <c r="J16" s="30" t="n">
-        <v>16.3</v>
+        <v>13.5</v>
       </c>
       <c r="K16" s="30" t="n">
-        <v>119</v>
+        <v>98</v>
       </c>
       <c r="L16" s="30" t="n">
         <v>69.2</v>
@@ -3575,22 +3575,22 @@
         <v>748</v>
       </c>
       <c r="F17" s="30" t="n">
-        <v>14.9</v>
+        <v>18</v>
       </c>
       <c r="G17" s="30" t="n">
-        <v>321</v>
+        <v>388</v>
       </c>
       <c r="H17" s="30" t="n">
-        <v>31.5</v>
+        <v>35.2</v>
       </c>
       <c r="I17" s="30" t="n">
-        <v>681</v>
+        <v>761</v>
       </c>
       <c r="J17" s="30" t="n">
-        <v>19</v>
+        <v>12.2</v>
       </c>
       <c r="K17" s="30" t="n">
-        <v>410</v>
+        <v>264</v>
       </c>
       <c r="L17" s="30" t="n">
         <v>65.40000000000001</v>
@@ -3931,22 +3931,22 @@
         <v>2733</v>
       </c>
       <c r="F19" s="30" t="n">
-        <v>26.7</v>
+        <v>29</v>
       </c>
       <c r="G19" s="30" t="n">
-        <v>1365</v>
+        <v>1481</v>
       </c>
       <c r="H19" s="30" t="n">
-        <v>7.9</v>
+        <v>10</v>
       </c>
       <c r="I19" s="30" t="n">
-        <v>401</v>
+        <v>509</v>
       </c>
       <c r="J19" s="30" t="n">
-        <v>11.9</v>
+        <v>7.5</v>
       </c>
       <c r="K19" s="30" t="n">
-        <v>609</v>
+        <v>385</v>
       </c>
       <c r="L19" s="30" t="n">
         <v>46.5</v>
@@ -4123,10 +4123,10 @@
         <v>2522</v>
       </c>
       <c r="F20" s="30" t="n">
-        <v>23.5</v>
+        <v>23.7</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>1093</v>
+        <v>1103</v>
       </c>
       <c r="H20" s="30" t="n">
         <v>17.1</v>
@@ -4135,10 +4135,10 @@
         <v>798</v>
       </c>
       <c r="J20" s="30" t="n">
-        <v>5.3</v>
+        <v>5.1</v>
       </c>
       <c r="K20" s="30" t="n">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="L20" s="30" t="n">
         <v>45.9</v>
@@ -4301,22 +4301,22 @@
         <v>2567</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>25.8</v>
+        <v>27.8</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>1300</v>
+        <v>1402</v>
       </c>
       <c r="H21" s="30" t="n">
-        <v>8.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="I21" s="30" t="n">
-        <v>407</v>
+        <v>417</v>
       </c>
       <c r="J21" s="30" t="n">
-        <v>15.3</v>
+        <v>13.1</v>
       </c>
       <c r="K21" s="30" t="n">
-        <v>772</v>
+        <v>661</v>
       </c>
       <c r="L21" s="30" t="n">
         <v>49.1</v>
@@ -4479,10 +4479,10 @@
         <v>14103</v>
       </c>
       <c r="F22" s="30" t="n">
-        <v>19.7</v>
+        <v>19.9</v>
       </c>
       <c r="G22" s="30" t="n">
-        <v>3987</v>
+        <v>4029</v>
       </c>
       <c r="H22" s="30" t="n">
         <v>2.2</v>
@@ -4491,10 +4491,10 @@
         <v>443</v>
       </c>
       <c r="J22" s="30" t="n">
-        <v>8.6</v>
+        <v>8.4</v>
       </c>
       <c r="K22" s="30" t="n">
-        <v>1737</v>
+        <v>1695</v>
       </c>
       <c r="L22" s="30" t="n">
         <v>30.4</v>
@@ -4657,10 +4657,10 @@
         <v>5435</v>
       </c>
       <c r="F23" s="30" t="n">
-        <v>16.7</v>
+        <v>18.5</v>
       </c>
       <c r="G23" s="30" t="n">
-        <v>1703</v>
+        <v>1887</v>
       </c>
       <c r="H23" s="30" t="n">
         <v>13.4</v>
@@ -4669,10 +4669,10 @@
         <v>1370</v>
       </c>
       <c r="J23" s="30" t="n">
-        <v>16.6</v>
+        <v>14.8</v>
       </c>
       <c r="K23" s="30" t="n">
-        <v>1693</v>
+        <v>1509</v>
       </c>
       <c r="L23" s="30" t="n">
         <v>46.7</v>
@@ -4835,22 +4835,22 @@
         <v>2558</v>
       </c>
       <c r="F24" s="30" t="n">
-        <v>25.3</v>
+        <v>26.4</v>
       </c>
       <c r="G24" s="30" t="n">
-        <v>2325</v>
+        <v>2422</v>
       </c>
       <c r="H24" s="30" t="n">
-        <v>21.6</v>
+        <v>24.3</v>
       </c>
       <c r="I24" s="30" t="n">
-        <v>1982</v>
+        <v>2228</v>
       </c>
       <c r="J24" s="30" t="n">
-        <v>25.2</v>
+        <v>21.5</v>
       </c>
       <c r="K24" s="30" t="n">
-        <v>2313</v>
+        <v>1970</v>
       </c>
       <c r="L24" s="30" t="n">
         <v>72.09999999999999</v>
@@ -5013,10 +5013,10 @@
         <v>687</v>
       </c>
       <c r="F25" s="30" t="n">
-        <v>27.4</v>
+        <v>29.1</v>
       </c>
       <c r="G25" s="30" t="n">
-        <v>496</v>
+        <v>528</v>
       </c>
       <c r="H25" s="30" t="n">
         <v>16.6</v>
@@ -5025,10 +5025,10 @@
         <v>300</v>
       </c>
       <c r="J25" s="30" t="n">
-        <v>18.2</v>
+        <v>16.4</v>
       </c>
       <c r="K25" s="30" t="n">
-        <v>329</v>
+        <v>297</v>
       </c>
       <c r="L25" s="30" t="n">
         <v>62.1</v>
@@ -5191,22 +5191,22 @@
         <v>1793</v>
       </c>
       <c r="F26" s="30" t="n">
-        <v>26.1</v>
+        <v>27</v>
       </c>
       <c r="G26" s="30" t="n">
-        <v>1144</v>
+        <v>1186</v>
       </c>
       <c r="H26" s="30" t="n">
-        <v>19.9</v>
+        <v>22.3</v>
       </c>
       <c r="I26" s="30" t="n">
-        <v>875</v>
+        <v>977</v>
       </c>
       <c r="J26" s="30" t="n">
-        <v>13.1</v>
+        <v>9.800000000000001</v>
       </c>
       <c r="K26" s="30" t="n">
-        <v>574</v>
+        <v>430</v>
       </c>
       <c r="L26" s="30" t="n">
         <v>59.1</v>
@@ -5369,22 +5369,22 @@
         <v>183</v>
       </c>
       <c r="F27" s="30" t="n">
-        <v>24.1</v>
+        <v>25.5</v>
       </c>
       <c r="G27" s="30" t="n">
-        <v>71</v>
+        <v>76</v>
       </c>
       <c r="H27" s="30" t="n">
-        <v>4.2</v>
+        <v>7.4</v>
       </c>
       <c r="I27" s="30" t="n">
-        <v>12</v>
+        <v>22</v>
       </c>
       <c r="J27" s="30" t="n">
-        <v>10.2</v>
+        <v>5.5</v>
       </c>
       <c r="K27" s="30" t="n">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="L27" s="30" t="n">
         <v>38.5</v>
@@ -5547,22 +5547,22 @@
         <v>237</v>
       </c>
       <c r="F28" s="30" t="n">
-        <v>15.4</v>
+        <v>17</v>
       </c>
       <c r="G28" s="30" t="n">
-        <v>69</v>
+        <v>76</v>
       </c>
       <c r="H28" s="30" t="n">
-        <v>19.2</v>
+        <v>21.9</v>
       </c>
       <c r="I28" s="30" t="n">
-        <v>86</v>
+        <v>98</v>
       </c>
       <c r="J28" s="30" t="n">
-        <v>12.3</v>
+        <v>8</v>
       </c>
       <c r="K28" s="30" t="n">
-        <v>55</v>
+        <v>36</v>
       </c>
       <c r="L28" s="30" t="n">
         <v>46.9</v>
@@ -5731,16 +5731,16 @@
         <v>90</v>
       </c>
       <c r="H29" s="30" t="n">
-        <v>10.1</v>
+        <v>11.6</v>
       </c>
       <c r="I29" s="30" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="J29" s="30" t="n">
-        <v>8.6</v>
+        <v>7.2</v>
       </c>
       <c r="K29" s="30" t="n">
-        <v>22</v>
+        <v>18</v>
       </c>
       <c r="L29" s="30" t="n">
         <v>54.1</v>
@@ -5903,22 +5903,22 @@
         <v>493</v>
       </c>
       <c r="F30" s="30" t="n">
-        <v>30.6</v>
+        <v>32.8</v>
       </c>
       <c r="G30" s="30" t="n">
-        <v>394</v>
+        <v>423</v>
       </c>
       <c r="H30" s="30" t="n">
-        <v>19.9</v>
+        <v>21.5</v>
       </c>
       <c r="I30" s="30" t="n">
-        <v>256</v>
+        <v>277</v>
       </c>
       <c r="J30" s="30" t="n">
-        <v>11.3</v>
+        <v>7.4</v>
       </c>
       <c r="K30" s="30" t="n">
-        <v>146</v>
+        <v>95</v>
       </c>
       <c r="L30" s="30" t="n">
         <v>61.7</v>
@@ -6081,10 +6081,10 @@
         <v>896</v>
       </c>
       <c r="F31" s="30" t="n">
-        <v>18.9</v>
+        <v>19.6</v>
       </c>
       <c r="G31" s="30" t="n">
-        <v>242</v>
+        <v>251</v>
       </c>
       <c r="H31" s="30" t="n">
         <v>6.8</v>
@@ -6093,10 +6093,10 @@
         <v>87</v>
       </c>
       <c r="J31" s="30" t="n">
-        <v>4.3</v>
+        <v>3.5</v>
       </c>
       <c r="K31" s="30" t="n">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="L31" s="30" t="n">
         <v>30</v>
@@ -6259,22 +6259,22 @@
         <v>2877</v>
       </c>
       <c r="F32" s="30" t="n">
-        <v>22.7</v>
+        <v>27.1</v>
       </c>
       <c r="G32" s="30" t="n">
-        <v>1148</v>
+        <v>1369</v>
       </c>
       <c r="H32" s="30" t="n">
-        <v>1.1</v>
+        <v>5.7</v>
       </c>
       <c r="I32" s="30" t="n">
-        <v>56</v>
+        <v>290</v>
       </c>
       <c r="J32" s="30" t="n">
-        <v>19.2</v>
+        <v>10.2</v>
       </c>
       <c r="K32" s="30" t="n">
-        <v>972</v>
+        <v>517</v>
       </c>
       <c r="L32" s="30" t="n">
         <v>43.1</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="N32" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O32" s="32" t="n">
@@ -6437,22 +6437,22 @@
         <v>585</v>
       </c>
       <c r="F33" s="30" t="n">
-        <v>29.9</v>
+        <v>36.3</v>
       </c>
       <c r="G33" s="30" t="n">
-        <v>409</v>
+        <v>496</v>
       </c>
       <c r="H33" s="30" t="n">
-        <v>6</v>
+        <v>6.8</v>
       </c>
       <c r="I33" s="30" t="n">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="J33" s="30" t="n">
-        <v>21.3</v>
+        <v>14.1</v>
       </c>
       <c r="K33" s="30" t="n">
-        <v>292</v>
+        <v>194</v>
       </c>
       <c r="L33" s="30" t="n">
         <v>57.2</v>
@@ -6462,7 +6462,7 @@
       </c>
       <c r="N33" s="31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O33" s="32" t="n">
@@ -6615,22 +6615,22 @@
         <v>546</v>
       </c>
       <c r="F34" s="30" t="n">
-        <v>19.2</v>
+        <v>20.2</v>
       </c>
       <c r="G34" s="30" t="n">
-        <v>581</v>
+        <v>610</v>
       </c>
       <c r="H34" s="30" t="n">
-        <v>37.7</v>
+        <v>48.8</v>
       </c>
       <c r="I34" s="30" t="n">
-        <v>1139</v>
+        <v>1475</v>
       </c>
       <c r="J34" s="30" t="n">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="K34" s="30" t="n">
-        <v>757</v>
+        <v>393</v>
       </c>
       <c r="L34" s="30" t="n">
         <v>81.90000000000001</v>
@@ -6640,7 +6640,7 @@
       </c>
       <c r="N34" s="31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O34" s="32" t="n">
@@ -6980,13 +6980,13 @@
         <v>1.5</v>
       </c>
       <c r="I36" s="30" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="J36" s="30" t="n">
-        <v>7</v>
+        <v>6.9</v>
       </c>
       <c r="K36" s="30" t="n">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="L36" s="30" t="n">
         <v>26.7</v>
@@ -7327,10 +7327,10 @@
         <v>14103</v>
       </c>
       <c r="F38" s="30" t="n">
-        <v>17</v>
+        <v>18.6</v>
       </c>
       <c r="G38" s="30" t="n">
-        <v>3674</v>
+        <v>4023</v>
       </c>
       <c r="H38" s="30" t="n">
         <v>9.199999999999999</v>
@@ -7339,10 +7339,10 @@
         <v>1984</v>
       </c>
       <c r="J38" s="30" t="n">
-        <v>8.6</v>
+        <v>7</v>
       </c>
       <c r="K38" s="30" t="n">
-        <v>1865</v>
+        <v>1516</v>
       </c>
       <c r="L38" s="30" t="n">
         <v>34.8</v>
@@ -7505,22 +7505,22 @@
         <v>1595</v>
       </c>
       <c r="F39" s="30" t="n">
-        <v>19.5</v>
+        <v>26.5</v>
       </c>
       <c r="G39" s="30" t="n">
-        <v>910</v>
+        <v>1236</v>
       </c>
       <c r="H39" s="30" t="n">
-        <v>20.4</v>
+        <v>26</v>
       </c>
       <c r="I39" s="30" t="n">
-        <v>950</v>
+        <v>1215</v>
       </c>
       <c r="J39" s="30" t="n">
-        <v>26</v>
+        <v>13.4</v>
       </c>
       <c r="K39" s="30" t="n">
-        <v>1215</v>
+        <v>624</v>
       </c>
       <c r="L39" s="30" t="n">
         <v>65.90000000000001</v>
@@ -7530,7 +7530,7 @@
       </c>
       <c r="N39" s="31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O39" s="32" t="n">
@@ -7683,22 +7683,22 @@
         <v>9241</v>
       </c>
       <c r="F40" s="30" t="n">
-        <v>13.6</v>
+        <v>14.2</v>
       </c>
       <c r="G40" s="30" t="n">
-        <v>1712</v>
+        <v>1781</v>
       </c>
       <c r="H40" s="30" t="n">
-        <v>4.6</v>
+        <v>5.2</v>
       </c>
       <c r="I40" s="30" t="n">
-        <v>580</v>
+        <v>648</v>
       </c>
       <c r="J40" s="30" t="n">
-        <v>8.199999999999999</v>
+        <v>7.1</v>
       </c>
       <c r="K40" s="30" t="n">
-        <v>1035</v>
+        <v>898</v>
       </c>
       <c r="L40" s="30" t="n">
         <v>26.5</v>
@@ -7861,22 +7861,22 @@
         <v>4589</v>
       </c>
       <c r="F41" s="30" t="n">
-        <v>24.2</v>
+        <v>24.9</v>
       </c>
       <c r="G41" s="30" t="n">
-        <v>1639</v>
+        <v>1681</v>
       </c>
       <c r="H41" s="30" t="n">
-        <v>2.2</v>
+        <v>2.3</v>
       </c>
       <c r="I41" s="30" t="n">
-        <v>147</v>
+        <v>152</v>
       </c>
       <c r="J41" s="30" t="n">
-        <v>5.7</v>
+        <v>5</v>
       </c>
       <c r="K41" s="30" t="n">
-        <v>389</v>
+        <v>341</v>
       </c>
       <c r="L41" s="30" t="n">
         <v>32.2</v>
@@ -8217,22 +8217,22 @@
         <v>8418</v>
       </c>
       <c r="F43" s="30" t="n">
-        <v>20.4</v>
+        <v>21.2</v>
       </c>
       <c r="G43" s="30" t="n">
-        <v>2752</v>
+        <v>2872</v>
       </c>
       <c r="H43" s="30" t="n">
-        <v>0.8</v>
+        <v>0.9</v>
       </c>
       <c r="I43" s="30" t="n">
-        <v>105</v>
+        <v>127</v>
       </c>
       <c r="J43" s="30" t="n">
-        <v>16.6</v>
+        <v>15.5</v>
       </c>
       <c r="K43" s="30" t="n">
-        <v>2242</v>
+        <v>2100</v>
       </c>
       <c r="L43" s="30" t="n">
         <v>37.7</v>
@@ -8401,16 +8401,16 @@
         <v>584</v>
       </c>
       <c r="H44" s="30" t="n">
-        <v>8.9</v>
+        <v>10.2</v>
       </c>
       <c r="I44" s="30" t="n">
-        <v>123</v>
+        <v>141</v>
       </c>
       <c r="J44" s="30" t="n">
-        <v>10.8</v>
+        <v>9.5</v>
       </c>
       <c r="K44" s="30" t="n">
-        <v>150</v>
+        <v>132</v>
       </c>
       <c r="L44" s="30" t="n">
         <v>61.7</v>
@@ -8573,22 +8573,22 @@
         <v>30</v>
       </c>
       <c r="F45" s="30" t="n">
-        <v>30</v>
+        <v>30.6</v>
       </c>
       <c r="G45" s="30" t="n">
         <v>25</v>
       </c>
       <c r="H45" s="30" t="n">
-        <v>17.1</v>
+        <v>20.6</v>
       </c>
       <c r="I45" s="30" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J45" s="30" t="n">
-        <v>16.5</v>
+        <v>12.5</v>
       </c>
       <c r="K45" s="30" t="n">
-        <v>14</v>
+        <v>10</v>
       </c>
       <c r="L45" s="30" t="n">
         <v>63.7</v>
@@ -9295,10 +9295,10 @@
         <v>3024</v>
       </c>
       <c r="F49" s="30" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="G49" s="30" t="n">
-        <v>809</v>
+        <v>817</v>
       </c>
       <c r="H49" s="30" t="n">
         <v>6</v>
@@ -9307,10 +9307,10 @@
         <v>260</v>
       </c>
       <c r="J49" s="30" t="n">
-        <v>6.1</v>
+        <v>5.9</v>
       </c>
       <c r="K49" s="30" t="n">
-        <v>266</v>
+        <v>259</v>
       </c>
       <c r="L49" s="30" t="n">
         <v>30.6</v>
@@ -9473,22 +9473,22 @@
         <v>5647</v>
       </c>
       <c r="F50" s="30" t="n">
-        <v>24.5</v>
+        <v>26</v>
       </c>
       <c r="G50" s="30" t="n">
-        <v>2771</v>
+        <v>2934</v>
       </c>
       <c r="H50" s="30" t="n">
-        <v>5.7</v>
+        <v>7.1</v>
       </c>
       <c r="I50" s="30" t="n">
-        <v>638</v>
+        <v>797</v>
       </c>
       <c r="J50" s="30" t="n">
-        <v>19.8</v>
+        <v>17</v>
       </c>
       <c r="K50" s="30" t="n">
-        <v>2239</v>
+        <v>1916</v>
       </c>
       <c r="L50" s="30" t="n">
         <v>50</v>
@@ -9829,10 +9829,10 @@
         <v>3400</v>
       </c>
       <c r="F52" s="30" t="n">
-        <v>31.3</v>
+        <v>32</v>
       </c>
       <c r="G52" s="30" t="n">
-        <v>2198</v>
+        <v>2245</v>
       </c>
       <c r="H52" s="30" t="n">
         <v>5.8</v>
@@ -9841,10 +9841,10 @@
         <v>407</v>
       </c>
       <c r="J52" s="30" t="n">
-        <v>14.4</v>
+        <v>13.8</v>
       </c>
       <c r="K52" s="30" t="n">
-        <v>1014</v>
+        <v>967</v>
       </c>
       <c r="L52" s="30" t="n">
         <v>51.6</v>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="N52" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O52" s="32" t="n">
@@ -10007,22 +10007,22 @@
         <v>174</v>
       </c>
       <c r="F53" s="30" t="n">
-        <v>36.7</v>
+        <v>36.9</v>
       </c>
       <c r="G53" s="30" t="n">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="H53" s="30" t="n">
-        <v>5.2</v>
+        <v>6</v>
       </c>
       <c r="I53" s="30" t="n">
-        <v>37</v>
+        <v>43</v>
       </c>
       <c r="J53" s="30" t="n">
-        <v>33.6</v>
+        <v>32.7</v>
       </c>
       <c r="K53" s="30" t="n">
-        <v>240</v>
+        <v>234</v>
       </c>
       <c r="L53" s="30" t="n">
         <v>75.59999999999999</v>
@@ -10205,22 +10205,22 @@
         <v>1006</v>
       </c>
       <c r="F54" s="30" t="n">
-        <v>20</v>
+        <v>20.2</v>
       </c>
       <c r="G54" s="30" t="n">
-        <v>306</v>
+        <v>309</v>
       </c>
       <c r="H54" s="30" t="n">
-        <v>3</v>
+        <v>3.8</v>
       </c>
       <c r="I54" s="30" t="n">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="J54" s="30" t="n">
-        <v>11.3</v>
+        <v>10.3</v>
       </c>
       <c r="K54" s="30" t="n">
-        <v>173</v>
+        <v>158</v>
       </c>
       <c r="L54" s="30" t="n">
         <v>34.3</v>
@@ -10561,22 +10561,22 @@
         <v>290</v>
       </c>
       <c r="F56" s="30" t="n">
-        <v>26.7</v>
+        <v>27.3</v>
       </c>
       <c r="G56" s="30" t="n">
-        <v>253</v>
+        <v>258</v>
       </c>
       <c r="H56" s="30" t="n">
-        <v>12</v>
+        <v>14.9</v>
       </c>
       <c r="I56" s="30" t="n">
-        <v>113</v>
+        <v>141</v>
       </c>
       <c r="J56" s="30" t="n">
-        <v>30.7</v>
+        <v>27.2</v>
       </c>
       <c r="K56" s="30" t="n">
-        <v>290</v>
+        <v>257</v>
       </c>
       <c r="L56" s="30" t="n">
         <v>69.40000000000001</v>
@@ -10739,22 +10739,22 @@
         <v>2349</v>
       </c>
       <c r="F57" s="30" t="n">
-        <v>20.2</v>
+        <v>20.7</v>
       </c>
       <c r="G57" s="30" t="n">
-        <v>752</v>
+        <v>771</v>
       </c>
       <c r="H57" s="30" t="n">
-        <v>3.6</v>
+        <v>4.4</v>
       </c>
       <c r="I57" s="30" t="n">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="J57" s="30" t="n">
-        <v>13.1</v>
+        <v>11.8</v>
       </c>
       <c r="K57" s="30" t="n">
-        <v>487</v>
+        <v>439</v>
       </c>
       <c r="L57" s="30" t="n">
         <v>36.9</v>
@@ -10917,22 +10917,22 @@
         <v>3969</v>
       </c>
       <c r="F58" s="30" t="n">
-        <v>24.9</v>
+        <v>25.4</v>
       </c>
       <c r="G58" s="30" t="n">
-        <v>1751</v>
+        <v>1783</v>
       </c>
       <c r="H58" s="30" t="n">
-        <v>9.5</v>
+        <v>10.3</v>
       </c>
       <c r="I58" s="30" t="n">
-        <v>668</v>
+        <v>722</v>
       </c>
       <c r="J58" s="30" t="n">
-        <v>9</v>
+        <v>7.8</v>
       </c>
       <c r="K58" s="30" t="n">
-        <v>633</v>
+        <v>547</v>
       </c>
       <c r="L58" s="30" t="n">
         <v>43.5</v>
@@ -11095,10 +11095,10 @@
         <v>2787</v>
       </c>
       <c r="F59" s="30" t="n">
-        <v>32.1</v>
+        <v>32.9</v>
       </c>
       <c r="G59" s="30" t="n">
-        <v>1661</v>
+        <v>1701</v>
       </c>
       <c r="H59" s="30" t="n">
         <v>4.9</v>
@@ -11107,10 +11107,10 @@
         <v>253</v>
       </c>
       <c r="J59" s="30" t="n">
-        <v>9.1</v>
+        <v>8.300000000000001</v>
       </c>
       <c r="K59" s="30" t="n">
-        <v>468</v>
+        <v>428</v>
       </c>
       <c r="L59" s="30" t="n">
         <v>46.1</v>
@@ -11469,22 +11469,22 @@
         <v>974</v>
       </c>
       <c r="F61" s="30" t="n">
-        <v>29.8</v>
+        <v>52.8</v>
       </c>
       <c r="G61" s="30" t="n">
-        <v>1219</v>
+        <v>2162</v>
       </c>
       <c r="H61" s="30" t="n">
-        <v>13.5</v>
+        <v>16</v>
       </c>
       <c r="I61" s="30" t="n">
-        <v>554</v>
+        <v>654</v>
       </c>
       <c r="J61" s="30" t="n">
-        <v>32.9</v>
+        <v>7.5</v>
       </c>
       <c r="K61" s="30" t="n">
-        <v>1350</v>
+        <v>308</v>
       </c>
       <c r="L61" s="30" t="n">
         <v>76.2</v>
@@ -11494,7 +11494,7 @@
       </c>
       <c r="N61" s="31" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O61" s="32" t="n">
@@ -11843,22 +11843,22 @@
         <v>234</v>
       </c>
       <c r="F63" s="30" t="n">
-        <v>25.4</v>
+        <v>28.2</v>
       </c>
       <c r="G63" s="30" t="n">
-        <v>140</v>
+        <v>156</v>
       </c>
       <c r="H63" s="30" t="n">
-        <v>18.3</v>
+        <v>19.7</v>
       </c>
       <c r="I63" s="30" t="n">
-        <v>101</v>
+        <v>109</v>
       </c>
       <c r="J63" s="30" t="n">
-        <v>14.1</v>
+        <v>9.9</v>
       </c>
       <c r="K63" s="30" t="n">
-        <v>78</v>
+        <v>54</v>
       </c>
       <c r="L63" s="30" t="n">
         <v>57.7</v>
@@ -12397,22 +12397,22 @@
         <v>20435</v>
       </c>
       <c r="F66" s="30" t="n">
-        <v>8</v>
+        <v>8.199999999999999</v>
       </c>
       <c r="G66" s="30" t="n">
-        <v>2804</v>
+        <v>2869</v>
       </c>
       <c r="H66" s="30" t="n">
-        <v>26.9</v>
+        <v>27.8</v>
       </c>
       <c r="I66" s="30" t="n">
-        <v>9459</v>
+        <v>9765</v>
       </c>
       <c r="J66" s="30" t="n">
-        <v>6.9</v>
+        <v>5.8</v>
       </c>
       <c r="K66" s="30" t="n">
-        <v>2416</v>
+        <v>2045</v>
       </c>
       <c r="L66" s="30" t="n">
         <v>41.8</v>

--- a/platform_PiN_output/Central_African_Republic___CAR/PiN_step1_Central_African_Republic___CAR_1009_08AM.xlsx
+++ b/platform_PiN_output/Central_African_Republic___CAR/PiN_step1_Central_African_Republic___CAR_1009_08AM.xlsx
@@ -1273,16 +1273,16 @@
         <v>547</v>
       </c>
       <c r="F4" s="30" t="n">
-        <v>47.9</v>
+        <v>49.3</v>
       </c>
       <c r="G4" s="30" t="n">
-        <v>817</v>
+        <v>841</v>
       </c>
       <c r="H4" s="30" t="n">
-        <v>11.6</v>
+        <v>10.2</v>
       </c>
       <c r="I4" s="30" t="n">
-        <v>197</v>
+        <v>174</v>
       </c>
       <c r="J4" s="30" t="n">
         <v>8.5</v>
@@ -1298,7 +1298,7 @@
       </c>
       <c r="N4" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O4" s="32" t="n">
@@ -1441,16 +1441,16 @@
         <v>1300</v>
       </c>
       <c r="F5" s="30" t="n">
-        <v>26.2</v>
+        <v>29.3</v>
       </c>
       <c r="G5" s="30" t="n">
-        <v>560</v>
+        <v>626</v>
       </c>
       <c r="H5" s="30" t="n">
-        <v>8.9</v>
+        <v>5.8</v>
       </c>
       <c r="I5" s="30" t="n">
-        <v>190</v>
+        <v>123</v>
       </c>
       <c r="J5" s="30" t="n">
         <v>4</v>
@@ -1609,16 +1609,16 @@
         <v>3829</v>
       </c>
       <c r="F6" s="30" t="n">
-        <v>26.2</v>
+        <v>26.4</v>
       </c>
       <c r="G6" s="30" t="n">
-        <v>1546</v>
+        <v>1554</v>
       </c>
       <c r="H6" s="30" t="n">
-        <v>1.4</v>
+        <v>1.2</v>
       </c>
       <c r="I6" s="30" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="J6" s="30" t="n">
         <v>7.4</v>
@@ -2329,16 +2329,16 @@
         <v>85</v>
       </c>
       <c r="F10" s="30" t="n">
-        <v>28</v>
+        <v>35.6</v>
       </c>
       <c r="G10" s="30" t="n">
-        <v>155</v>
+        <v>198</v>
       </c>
       <c r="H10" s="30" t="n">
-        <v>19</v>
+        <v>11.4</v>
       </c>
       <c r="I10" s="30" t="n">
-        <v>106</v>
+        <v>63</v>
       </c>
       <c r="J10" s="30" t="n">
         <v>37.7</v>
@@ -3041,16 +3041,16 @@
         <v>3491</v>
       </c>
       <c r="F14" s="30" t="n">
-        <v>11.8</v>
+        <v>16.2</v>
       </c>
       <c r="G14" s="30" t="n">
-        <v>775</v>
+        <v>1064</v>
       </c>
       <c r="H14" s="30" t="n">
-        <v>15.5</v>
+        <v>11.1</v>
       </c>
       <c r="I14" s="30" t="n">
-        <v>1020</v>
+        <v>731</v>
       </c>
       <c r="J14" s="30" t="n">
         <v>19.4</v>
@@ -3219,16 +3219,16 @@
         <v>3348</v>
       </c>
       <c r="F15" s="30" t="n">
-        <v>16.3</v>
+        <v>18.4</v>
       </c>
       <c r="G15" s="30" t="n">
-        <v>923</v>
+        <v>1041</v>
       </c>
       <c r="H15" s="30" t="n">
-        <v>8.5</v>
+        <v>6.4</v>
       </c>
       <c r="I15" s="30" t="n">
-        <v>482</v>
+        <v>364</v>
       </c>
       <c r="J15" s="30" t="n">
         <v>16.2</v>
@@ -3397,16 +3397,16 @@
         <v>224</v>
       </c>
       <c r="F16" s="30" t="n">
-        <v>21.5</v>
+        <v>39.4</v>
       </c>
       <c r="G16" s="30" t="n">
-        <v>157</v>
+        <v>286</v>
       </c>
       <c r="H16" s="30" t="n">
-        <v>34.2</v>
+        <v>16.3</v>
       </c>
       <c r="I16" s="30" t="n">
-        <v>248</v>
+        <v>119</v>
       </c>
       <c r="J16" s="30" t="n">
         <v>13.5</v>
@@ -3575,16 +3575,16 @@
         <v>748</v>
       </c>
       <c r="F17" s="30" t="n">
-        <v>18</v>
+        <v>33.2</v>
       </c>
       <c r="G17" s="30" t="n">
-        <v>388</v>
+        <v>717</v>
       </c>
       <c r="H17" s="30" t="n">
-        <v>35.2</v>
+        <v>20</v>
       </c>
       <c r="I17" s="30" t="n">
-        <v>761</v>
+        <v>432</v>
       </c>
       <c r="J17" s="30" t="n">
         <v>12.2</v>
@@ -3753,16 +3753,16 @@
         <v>4496</v>
       </c>
       <c r="F18" s="30" t="n">
-        <v>48.6</v>
+        <v>51.2</v>
       </c>
       <c r="G18" s="30" t="n">
-        <v>5875</v>
+        <v>6199</v>
       </c>
       <c r="H18" s="30" t="n">
-        <v>8.699999999999999</v>
+        <v>6.1</v>
       </c>
       <c r="I18" s="30" t="n">
-        <v>1058</v>
+        <v>734</v>
       </c>
       <c r="J18" s="30" t="n">
         <v>5.5</v>
@@ -3931,16 +3931,16 @@
         <v>2733</v>
       </c>
       <c r="F19" s="30" t="n">
-        <v>29</v>
+        <v>30.3</v>
       </c>
       <c r="G19" s="30" t="n">
-        <v>1481</v>
+        <v>1547</v>
       </c>
       <c r="H19" s="30" t="n">
-        <v>10</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="I19" s="30" t="n">
-        <v>509</v>
+        <v>443</v>
       </c>
       <c r="J19" s="30" t="n">
         <v>7.5</v>
@@ -4123,16 +4123,16 @@
         <v>2522</v>
       </c>
       <c r="F20" s="30" t="n">
-        <v>23.7</v>
+        <v>37</v>
       </c>
       <c r="G20" s="30" t="n">
-        <v>1103</v>
+        <v>1724</v>
       </c>
       <c r="H20" s="30" t="n">
-        <v>17.1</v>
+        <v>3.8</v>
       </c>
       <c r="I20" s="30" t="n">
-        <v>798</v>
+        <v>178</v>
       </c>
       <c r="J20" s="30" t="n">
         <v>5.1</v>
@@ -4148,7 +4148,7 @@
       </c>
       <c r="N20" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O20" s="32" t="n">
@@ -4301,16 +4301,16 @@
         <v>2567</v>
       </c>
       <c r="F21" s="30" t="n">
-        <v>27.8</v>
+        <v>30.3</v>
       </c>
       <c r="G21" s="30" t="n">
-        <v>1402</v>
+        <v>1529</v>
       </c>
       <c r="H21" s="30" t="n">
-        <v>8.300000000000001</v>
+        <v>5.7</v>
       </c>
       <c r="I21" s="30" t="n">
-        <v>417</v>
+        <v>290</v>
       </c>
       <c r="J21" s="30" t="n">
         <v>13.1</v>
@@ -4326,7 +4326,7 @@
       </c>
       <c r="N21" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O21" s="32" t="n">
@@ -4479,16 +4479,16 @@
         <v>14103</v>
       </c>
       <c r="F22" s="30" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="G22" s="30" t="n">
-        <v>4029</v>
+        <v>4058</v>
       </c>
       <c r="H22" s="30" t="n">
-        <v>2.2</v>
+        <v>2</v>
       </c>
       <c r="I22" s="30" t="n">
-        <v>443</v>
+        <v>414</v>
       </c>
       <c r="J22" s="30" t="n">
         <v>8.4</v>
@@ -4657,16 +4657,16 @@
         <v>5435</v>
       </c>
       <c r="F23" s="30" t="n">
-        <v>18.5</v>
+        <v>24.7</v>
       </c>
       <c r="G23" s="30" t="n">
-        <v>1887</v>
+        <v>2519</v>
       </c>
       <c r="H23" s="30" t="n">
-        <v>13.4</v>
+        <v>7.2</v>
       </c>
       <c r="I23" s="30" t="n">
-        <v>1370</v>
+        <v>738</v>
       </c>
       <c r="J23" s="30" t="n">
         <v>14.8</v>
@@ -4835,16 +4835,16 @@
         <v>2558</v>
       </c>
       <c r="F24" s="30" t="n">
-        <v>26.4</v>
+        <v>43.2</v>
       </c>
       <c r="G24" s="30" t="n">
-        <v>2422</v>
+        <v>3962</v>
       </c>
       <c r="H24" s="30" t="n">
-        <v>24.3</v>
+        <v>7.5</v>
       </c>
       <c r="I24" s="30" t="n">
-        <v>2228</v>
+        <v>688</v>
       </c>
       <c r="J24" s="30" t="n">
         <v>21.5</v>
@@ -5013,16 +5013,16 @@
         <v>687</v>
       </c>
       <c r="F25" s="30" t="n">
-        <v>29.1</v>
+        <v>39.6</v>
       </c>
       <c r="G25" s="30" t="n">
-        <v>528</v>
+        <v>718</v>
       </c>
       <c r="H25" s="30" t="n">
-        <v>16.6</v>
+        <v>6.1</v>
       </c>
       <c r="I25" s="30" t="n">
-        <v>300</v>
+        <v>110</v>
       </c>
       <c r="J25" s="30" t="n">
         <v>16.4</v>
@@ -5191,16 +5191,16 @@
         <v>1793</v>
       </c>
       <c r="F26" s="30" t="n">
-        <v>27</v>
+        <v>35.4</v>
       </c>
       <c r="G26" s="30" t="n">
-        <v>1186</v>
+        <v>1553</v>
       </c>
       <c r="H26" s="30" t="n">
-        <v>22.3</v>
+        <v>13.9</v>
       </c>
       <c r="I26" s="30" t="n">
-        <v>977</v>
+        <v>610</v>
       </c>
       <c r="J26" s="30" t="n">
         <v>9.800000000000001</v>
@@ -5369,16 +5369,16 @@
         <v>183</v>
       </c>
       <c r="F27" s="30" t="n">
-        <v>25.5</v>
+        <v>25.2</v>
       </c>
       <c r="G27" s="30" t="n">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="H27" s="30" t="n">
-        <v>7.4</v>
+        <v>7.8</v>
       </c>
       <c r="I27" s="30" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="J27" s="30" t="n">
         <v>5.5</v>
@@ -5547,16 +5547,16 @@
         <v>237</v>
       </c>
       <c r="F28" s="30" t="n">
-        <v>17</v>
+        <v>24.3</v>
       </c>
       <c r="G28" s="30" t="n">
-        <v>76</v>
+        <v>109</v>
       </c>
       <c r="H28" s="30" t="n">
-        <v>21.9</v>
+        <v>14.6</v>
       </c>
       <c r="I28" s="30" t="n">
-        <v>98</v>
+        <v>65</v>
       </c>
       <c r="J28" s="30" t="n">
         <v>8</v>
@@ -5725,16 +5725,16 @@
         <v>117</v>
       </c>
       <c r="F29" s="30" t="n">
-        <v>35.4</v>
+        <v>37</v>
       </c>
       <c r="G29" s="30" t="n">
-        <v>90</v>
+        <v>94</v>
       </c>
       <c r="H29" s="30" t="n">
-        <v>11.6</v>
+        <v>9.9</v>
       </c>
       <c r="I29" s="30" t="n">
-        <v>29</v>
+        <v>25</v>
       </c>
       <c r="J29" s="30" t="n">
         <v>7.2</v>
@@ -5903,16 +5903,16 @@
         <v>493</v>
       </c>
       <c r="F30" s="30" t="n">
-        <v>32.8</v>
+        <v>41.7</v>
       </c>
       <c r="G30" s="30" t="n">
-        <v>423</v>
+        <v>537</v>
       </c>
       <c r="H30" s="30" t="n">
-        <v>21.5</v>
+        <v>12.7</v>
       </c>
       <c r="I30" s="30" t="n">
-        <v>277</v>
+        <v>163</v>
       </c>
       <c r="J30" s="30" t="n">
         <v>7.4</v>
@@ -6081,16 +6081,16 @@
         <v>896</v>
       </c>
       <c r="F31" s="30" t="n">
-        <v>19.6</v>
+        <v>23.6</v>
       </c>
       <c r="G31" s="30" t="n">
-        <v>251</v>
+        <v>302</v>
       </c>
       <c r="H31" s="30" t="n">
-        <v>6.8</v>
+        <v>2.9</v>
       </c>
       <c r="I31" s="30" t="n">
-        <v>87</v>
+        <v>37</v>
       </c>
       <c r="J31" s="30" t="n">
         <v>3.5</v>
@@ -6259,16 +6259,16 @@
         <v>2877</v>
       </c>
       <c r="F32" s="30" t="n">
-        <v>27.1</v>
+        <v>22.7</v>
       </c>
       <c r="G32" s="30" t="n">
-        <v>1369</v>
+        <v>1148</v>
       </c>
       <c r="H32" s="30" t="n">
-        <v>5.7</v>
+        <v>10.1</v>
       </c>
       <c r="I32" s="30" t="n">
-        <v>290</v>
+        <v>511</v>
       </c>
       <c r="J32" s="30" t="n">
         <v>10.2</v>
@@ -6284,7 +6284,7 @@
       </c>
       <c r="N32" s="31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O32" s="32" t="n">
@@ -6437,16 +6437,16 @@
         <v>585</v>
       </c>
       <c r="F33" s="30" t="n">
-        <v>36.3</v>
+        <v>30.6</v>
       </c>
       <c r="G33" s="30" t="n">
-        <v>496</v>
+        <v>418</v>
       </c>
       <c r="H33" s="30" t="n">
-        <v>6.8</v>
+        <v>12.5</v>
       </c>
       <c r="I33" s="30" t="n">
-        <v>93</v>
+        <v>172</v>
       </c>
       <c r="J33" s="30" t="n">
         <v>14.1</v>
@@ -6615,16 +6615,16 @@
         <v>546</v>
       </c>
       <c r="F34" s="30" t="n">
-        <v>20.2</v>
+        <v>28.5</v>
       </c>
       <c r="G34" s="30" t="n">
-        <v>610</v>
+        <v>862</v>
       </c>
       <c r="H34" s="30" t="n">
-        <v>48.8</v>
+        <v>40.4</v>
       </c>
       <c r="I34" s="30" t="n">
-        <v>1475</v>
+        <v>1222</v>
       </c>
       <c r="J34" s="30" t="n">
         <v>13</v>
@@ -6793,16 +6793,16 @@
         <v>6361</v>
       </c>
       <c r="F35" s="30" t="n">
-        <v>21.5</v>
+        <v>24.1</v>
       </c>
       <c r="G35" s="30" t="n">
-        <v>2224</v>
+        <v>2502</v>
       </c>
       <c r="H35" s="30" t="n">
-        <v>5.4</v>
+        <v>2.7</v>
       </c>
       <c r="I35" s="30" t="n">
-        <v>559</v>
+        <v>281</v>
       </c>
       <c r="J35" s="30" t="n">
         <v>11.8</v>
@@ -6971,16 +6971,16 @@
         <v>1522</v>
       </c>
       <c r="F36" s="30" t="n">
-        <v>18.3</v>
+        <v>18.5</v>
       </c>
       <c r="G36" s="30" t="n">
-        <v>380</v>
+        <v>385</v>
       </c>
       <c r="H36" s="30" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="I36" s="30" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="J36" s="30" t="n">
         <v>6.9</v>
@@ -7327,16 +7327,16 @@
         <v>14103</v>
       </c>
       <c r="F38" s="30" t="n">
-        <v>18.6</v>
+        <v>20.6</v>
       </c>
       <c r="G38" s="30" t="n">
-        <v>4023</v>
+        <v>4461</v>
       </c>
       <c r="H38" s="30" t="n">
-        <v>9.199999999999999</v>
+        <v>7.2</v>
       </c>
       <c r="I38" s="30" t="n">
-        <v>1984</v>
+        <v>1547</v>
       </c>
       <c r="J38" s="30" t="n">
         <v>7</v>
@@ -7505,16 +7505,16 @@
         <v>1595</v>
       </c>
       <c r="F39" s="30" t="n">
-        <v>26.5</v>
+        <v>22</v>
       </c>
       <c r="G39" s="30" t="n">
-        <v>1236</v>
+        <v>1029</v>
       </c>
       <c r="H39" s="30" t="n">
-        <v>26</v>
+        <v>30.5</v>
       </c>
       <c r="I39" s="30" t="n">
-        <v>1215</v>
+        <v>1422</v>
       </c>
       <c r="J39" s="30" t="n">
         <v>13.4</v>
@@ -7683,16 +7683,16 @@
         <v>9241</v>
       </c>
       <c r="F40" s="30" t="n">
-        <v>14.2</v>
+        <v>16.3</v>
       </c>
       <c r="G40" s="30" t="n">
-        <v>1781</v>
+        <v>2055</v>
       </c>
       <c r="H40" s="30" t="n">
-        <v>5.2</v>
+        <v>3</v>
       </c>
       <c r="I40" s="30" t="n">
-        <v>648</v>
+        <v>374</v>
       </c>
       <c r="J40" s="30" t="n">
         <v>7.1</v>
@@ -7861,16 +7861,16 @@
         <v>4589</v>
       </c>
       <c r="F41" s="30" t="n">
-        <v>24.9</v>
+        <v>25.6</v>
       </c>
       <c r="G41" s="30" t="n">
-        <v>1681</v>
+        <v>1733</v>
       </c>
       <c r="H41" s="30" t="n">
-        <v>2.3</v>
+        <v>1.5</v>
       </c>
       <c r="I41" s="30" t="n">
-        <v>152</v>
+        <v>100</v>
       </c>
       <c r="J41" s="30" t="n">
         <v>5</v>
@@ -8039,16 +8039,16 @@
         <v>573</v>
       </c>
       <c r="F42" s="30" t="n">
-        <v>37.7</v>
+        <v>37.9</v>
       </c>
       <c r="G42" s="30" t="n">
-        <v>371</v>
+        <v>373</v>
       </c>
       <c r="H42" s="30" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="I42" s="30" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="J42" s="30" t="n">
         <v>3.3</v>
@@ -8217,16 +8217,16 @@
         <v>8418</v>
       </c>
       <c r="F43" s="30" t="n">
-        <v>21.2</v>
+        <v>20.8</v>
       </c>
       <c r="G43" s="30" t="n">
-        <v>2872</v>
+        <v>2815</v>
       </c>
       <c r="H43" s="30" t="n">
-        <v>0.9</v>
+        <v>1.4</v>
       </c>
       <c r="I43" s="30" t="n">
-        <v>127</v>
+        <v>184</v>
       </c>
       <c r="J43" s="30" t="n">
         <v>15.5</v>
@@ -8395,16 +8395,16 @@
         <v>531</v>
       </c>
       <c r="F44" s="30" t="n">
-        <v>42.1</v>
+        <v>47.2</v>
       </c>
       <c r="G44" s="30" t="n">
-        <v>584</v>
+        <v>654</v>
       </c>
       <c r="H44" s="30" t="n">
-        <v>10.2</v>
+        <v>5.1</v>
       </c>
       <c r="I44" s="30" t="n">
-        <v>141</v>
+        <v>70</v>
       </c>
       <c r="J44" s="30" t="n">
         <v>9.5</v>
@@ -8573,16 +8573,16 @@
         <v>30</v>
       </c>
       <c r="F45" s="30" t="n">
-        <v>30.6</v>
+        <v>37.3</v>
       </c>
       <c r="G45" s="30" t="n">
-        <v>25</v>
+        <v>31</v>
       </c>
       <c r="H45" s="30" t="n">
-        <v>20.6</v>
+        <v>13.9</v>
       </c>
       <c r="I45" s="30" t="n">
-        <v>17</v>
+        <v>11</v>
       </c>
       <c r="J45" s="30" t="n">
         <v>12.5</v>
@@ -8949,16 +8949,16 @@
         <v>1575</v>
       </c>
       <c r="F47" s="30" t="n">
-        <v>23.6</v>
+        <v>28.1</v>
       </c>
       <c r="G47" s="30" t="n">
-        <v>1041</v>
+        <v>1237</v>
       </c>
       <c r="H47" s="30" t="n">
-        <v>11.1</v>
+        <v>6.7</v>
       </c>
       <c r="I47" s="30" t="n">
-        <v>490</v>
+        <v>293</v>
       </c>
       <c r="J47" s="30" t="n">
         <v>29.5</v>
@@ -9295,16 +9295,16 @@
         <v>3024</v>
       </c>
       <c r="F49" s="30" t="n">
-        <v>18.7</v>
+        <v>19.1</v>
       </c>
       <c r="G49" s="30" t="n">
-        <v>817</v>
+        <v>832</v>
       </c>
       <c r="H49" s="30" t="n">
-        <v>6</v>
+        <v>5.6</v>
       </c>
       <c r="I49" s="30" t="n">
-        <v>260</v>
+        <v>244</v>
       </c>
       <c r="J49" s="30" t="n">
         <v>5.9</v>
@@ -9473,16 +9473,16 @@
         <v>5647</v>
       </c>
       <c r="F50" s="30" t="n">
-        <v>26</v>
+        <v>29.2</v>
       </c>
       <c r="G50" s="30" t="n">
-        <v>2934</v>
+        <v>3301</v>
       </c>
       <c r="H50" s="30" t="n">
-        <v>7.1</v>
+        <v>3.8</v>
       </c>
       <c r="I50" s="30" t="n">
-        <v>797</v>
+        <v>430</v>
       </c>
       <c r="J50" s="30" t="n">
         <v>17</v>
@@ -9829,16 +9829,16 @@
         <v>3400</v>
       </c>
       <c r="F52" s="30" t="n">
-        <v>32</v>
+        <v>31.4</v>
       </c>
       <c r="G52" s="30" t="n">
-        <v>2245</v>
+        <v>2205</v>
       </c>
       <c r="H52" s="30" t="n">
-        <v>5.8</v>
+        <v>6.4</v>
       </c>
       <c r="I52" s="30" t="n">
-        <v>407</v>
+        <v>447</v>
       </c>
       <c r="J52" s="30" t="n">
         <v>13.8</v>
@@ -9854,7 +9854,7 @@
       </c>
       <c r="N52" s="31" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="O52" s="32" t="n">
@@ -10007,16 +10007,16 @@
         <v>174</v>
       </c>
       <c r="F53" s="30" t="n">
-        <v>36.9</v>
+        <v>41.3</v>
       </c>
       <c r="G53" s="30" t="n">
-        <v>263</v>
+        <v>295</v>
       </c>
       <c r="H53" s="30" t="n">
-        <v>6</v>
+        <v>1.5</v>
       </c>
       <c r="I53" s="30" t="n">
-        <v>43</v>
+        <v>11</v>
       </c>
       <c r="J53" s="30" t="n">
         <v>32.7</v>
@@ -10561,16 +10561,16 @@
         <v>290</v>
       </c>
       <c r="F56" s="30" t="n">
-        <v>27.3</v>
+        <v>31.3</v>
       </c>
       <c r="G56" s="30" t="n">
-        <v>258</v>
+        <v>296</v>
       </c>
       <c r="H56" s="30" t="n">
-        <v>14.9</v>
+        <v>10.8</v>
       </c>
       <c r="I56" s="30" t="n">
-        <v>141</v>
+        <v>102</v>
       </c>
       <c r="J56" s="30" t="n">
         <v>27.2</v>
@@ -10739,16 +10739,16 @@
         <v>2349</v>
       </c>
       <c r="F57" s="30" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="G57" s="30" t="n">
-        <v>771</v>
+        <v>774</v>
       </c>
       <c r="H57" s="30" t="n">
-        <v>4.4</v>
+        <v>4.3</v>
       </c>
       <c r="I57" s="30" t="n">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="J57" s="30" t="n">
         <v>11.8</v>
@@ -10917,16 +10917,16 @@
         <v>3969</v>
       </c>
       <c r="F58" s="30" t="n">
-        <v>25.4</v>
+        <v>28.8</v>
       </c>
       <c r="G58" s="30" t="n">
-        <v>1783</v>
+        <v>2024</v>
       </c>
       <c r="H58" s="30" t="n">
-        <v>10.3</v>
+        <v>6.8</v>
       </c>
       <c r="I58" s="30" t="n">
-        <v>722</v>
+        <v>480</v>
       </c>
       <c r="J58" s="30" t="n">
         <v>7.8</v>
@@ -11469,16 +11469,16 @@
         <v>974</v>
       </c>
       <c r="F61" s="30" t="n">
-        <v>52.8</v>
+        <v>30.3</v>
       </c>
       <c r="G61" s="30" t="n">
-        <v>2162</v>
+        <v>1241</v>
       </c>
       <c r="H61" s="30" t="n">
-        <v>16</v>
+        <v>38.4</v>
       </c>
       <c r="I61" s="30" t="n">
-        <v>654</v>
+        <v>1575</v>
       </c>
       <c r="J61" s="30" t="n">
         <v>7.5</v>
@@ -11843,16 +11843,16 @@
         <v>234</v>
       </c>
       <c r="F63" s="30" t="n">
-        <v>28.2</v>
+        <v>25.4</v>
       </c>
       <c r="G63" s="30" t="n">
-        <v>156</v>
+        <v>140</v>
       </c>
       <c r="H63" s="30" t="n">
-        <v>19.7</v>
+        <v>22.5</v>
       </c>
       <c r="I63" s="30" t="n">
-        <v>109</v>
+        <v>125</v>
       </c>
       <c r="J63" s="30" t="n">
         <v>9.9</v>
@@ -12397,16 +12397,16 @@
         <v>20435</v>
       </c>
       <c r="F66" s="30" t="n">
-        <v>8.199999999999999</v>
+        <v>33.4</v>
       </c>
       <c r="G66" s="30" t="n">
-        <v>2869</v>
+        <v>11723</v>
       </c>
       <c r="H66" s="30" t="n">
-        <v>27.8</v>
+        <v>2.6</v>
       </c>
       <c r="I66" s="30" t="n">
-        <v>9765</v>
+        <v>911</v>
       </c>
       <c r="J66" s="30" t="n">
         <v>5.8</v>
@@ -12422,7 +12422,7 @@
       </c>
       <c r="N66" s="31" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>3</t>
         </is>
       </c>
       <c r="O66" s="32" t="n">
